--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:53:12+00:00</t>
+    <t>2026-08-20T15:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:08:45+00:00</t>
+    <t>2026-08-20T15:24:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:24:46+00:00</t>
+    <t>2026-08-21T08:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T08:13:05+00:00</t>
+    <t>2026-08-23T21:45:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-23T21:45:18+00:00</t>
+    <t>2026-08-24T13:13:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T13:13:01+00:00</t>
+    <t>2026-08-25T11:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -359,7 +359,16 @@
     <t>FRLMSection.subSection</t>
   </si>
   <si>
-    <t>FRLMExposureInformation.subSection.quantityExposure</t>
+    <t>FRLMExposureInformation.entry</t>
+  </si>
+  <si>
+    <t>Entrées</t>
+  </si>
+  <si>
+    <t>FRLMSection.entry</t>
+  </si>
+  <si>
+    <t>FRLMExposureInformation.entry.quantityExposure</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMQuantityExposure
@@ -369,7 +378,7 @@
     <t>Entrée Quantité</t>
   </si>
   <si>
-    <t>FRLMExposureInformation.subSection.radiopharmaceuticalAdministration</t>
+    <t>FRLMExposureInformation.entry.radiopharmaceuticalAdministration</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedicationAdministration
@@ -377,15 +386,6 @@
   </si>
   <si>
     <t>Entrée administration des produits radiopharmaceutiques</t>
-  </si>
-  <si>
-    <t>FRLMExposureInformation.entry</t>
-  </si>
-  <si>
-    <t>Entrées</t>
-  </si>
-  <si>
-    <t>FRLMSection.entry</t>
   </si>
 </sst>
 </file>
@@ -690,8 +690,8 @@
   <dimension ref="A1:AJ14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="58.98828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="58.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="54.4921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="54.4921875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -721,7 +721,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="58.98828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="54.4921875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1865,13 +1865,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>114</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1922,7 +1922,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -1953,7 +1953,7 @@
         <v>73</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>72</v>
@@ -2028,7 +2028,7 @@
         <v>73</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>72</v>
@@ -2053,7 +2053,7 @@
         <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>72</v>
@@ -2065,13 +2065,13 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2122,13 +2122,13 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>72</v>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:34:21+00:00</t>
+    <t>2026-08-25T11:56:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:56:50+00:00</t>
+    <t>2026-08-25T20:08:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMExposureInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T20:08:46+00:00</t>
+    <t>2026-08-31T08:09:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
